--- a/tame_output/MOZAIC/data/universe_last2023-08-04.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-04.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.0453681589252</v>
+        <v>567.4936444427473</v>
       </c>
       <c r="E2" t="n">
-        <v>12499.40484773576</v>
+        <v>12262.48854787877</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5932456694721657</v>
+        <v>0.5960126888649786</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4931062767350548</v>
+        <v>0.4931011992861996</v>
       </c>
       <c r="H2" t="n">
-        <v>1.203078722502078</v>
+        <v>1.208702574091791</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>220.0721040484799</v>
+        <v>220.6613444177853</v>
       </c>
       <c r="E3" t="n">
-        <v>4635.031673729335</v>
+        <v>4547.455237789544</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2225530141682812</v>
+        <v>0.2285719991414028</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5908666882316934</v>
+        <v>0.5908553155847328</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3766552059895661</v>
+        <v>0.3868493573848943</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907370614745367</v>
+        <v>0.8907309152877282</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067329463099642</v>
+        <v>1.067312545204223</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.16851723133261</v>
+        <v>37.23187192500801</v>
       </c>
       <c r="E4" t="n">
-        <v>407.0298572627681</v>
+        <v>399.0629505598425</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3246300148199273</v>
+        <v>-0.3224208869507588</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5562047341352612</v>
+        <v>0.5562326512300044</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5836520167787386</v>
+        <v>-0.579651133815653</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7370148613012416</v>
+        <v>0.7369981739681813</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8313241471960592</v>
+        <v>0.8313556098655112</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34.77721041208655</v>
+        <v>34.84155883497539</v>
       </c>
       <c r="E5" t="n">
-        <v>1347.382163236932</v>
+        <v>1189.695302143153</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5872657783247688</v>
+        <v>0.5971118518413923</v>
       </c>
       <c r="G5" t="n">
-        <v>1.09611871329818</v>
+        <v>1.09608356074647</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5357684082937589</v>
+        <v>0.5447685497944509</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4743886602804545</v>
+        <v>0.4743722328466547</v>
       </c>
       <c r="N5" t="n">
-        <v>1.054511598093582</v>
+        <v>1.054452122303663</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.39299053574852</v>
+        <v>10.42292453444059</v>
       </c>
       <c r="E6" t="n">
-        <v>366.6952197844439</v>
+        <v>332.3116084024765</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5089210427911633</v>
+        <v>-0.5054178925642967</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8077865437928813</v>
+        <v>0.8078636145023161</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6300192132460827</v>
+        <v>-0.6256227950997137</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6671601010474369</v>
+        <v>0.6671152459309835</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09291440325993</v>
+        <v>1.092956445142617</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.25074138700945</v>
+        <v>10.27455902691923</v>
       </c>
       <c r="E7" t="n">
-        <v>294.0620253010072</v>
+        <v>284.7715639480708</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3497715159552751</v>
+        <v>-0.3456674819209137</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7078714006280574</v>
+        <v>0.7079059188228215</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4941173151577265</v>
+        <v>-0.4882957928868923</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7503688579492841</v>
+        <v>0.7503331456014539</v>
       </c>
       <c r="N7" t="n">
-        <v>1.077180882752441</v>
+        <v>1.077193232604415</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.261861685831123</v>
+        <v>9.279763948836955</v>
       </c>
       <c r="E8" t="n">
-        <v>353.3724151108309</v>
+        <v>332.9519268799259</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3721695108536669</v>
+        <v>-0.3685496608853822</v>
       </c>
       <c r="G8" t="n">
-        <v>1.159022099599991</v>
+        <v>1.159078031484617</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3211064836314272</v>
+        <v>-0.317967945965917</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7373913840027749</v>
+        <v>0.7373825456542384</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733202253625018</v>
+        <v>1.733282966468644</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.944281729020461</v>
+        <v>6.951985251490613</v>
       </c>
       <c r="E9" t="n">
-        <v>173.3612793809318</v>
+        <v>175.6766051158071</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3072188607719533</v>
+        <v>0.3118877084735936</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4801830075532303</v>
+        <v>0.4802207050252142</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6397953612256817</v>
+        <v>0.6494674328072084</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6738906222977205</v>
+        <v>0.6738597909511426</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6562293790283718</v>
+        <v>0.6562576289961132</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.206283956163727</v>
+        <v>6.214101503947482</v>
       </c>
       <c r="E10" t="n">
-        <v>289.2311860880612</v>
+        <v>281.3587070836348</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3311182298784168</v>
+        <v>-0.3272731217324214</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9482814724412755</v>
+        <v>0.9482714351222369</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3491771583662593</v>
+        <v>-0.345125994109729</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7137217428653608</v>
+        <v>0.7137128167814666</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372542060748024</v>
+        <v>1.372524500070581</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.088366639618607</v>
+        <v>6.096350869484572</v>
       </c>
       <c r="E11" t="n">
-        <v>664.5307905526529</v>
+        <v>634.0259415106566</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7131657367221476</v>
+        <v>0.7224447427470615</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8190129544709044</v>
+        <v>0.8190282832630276</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8707624620942219</v>
+        <v>0.8820754514957957</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.662303294150872</v>
+        <v>0.6622882721764796</v>
       </c>
       <c r="N11" t="n">
-        <v>1.100036651915845</v>
+        <v>1.100043616545955</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.048795618747878</v>
+        <v>6.044602292046744</v>
       </c>
       <c r="E12" t="n">
-        <v>105.0972437835275</v>
+        <v>102.6442912919572</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3105970771237854</v>
+        <v>-0.3089588336275628</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6517890630809555</v>
+        <v>0.6518033200143509</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4765300535354451</v>
+        <v>-0.4740062287819589</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7891592815362939</v>
+        <v>0.7891605213836451</v>
       </c>
       <c r="N12" t="n">
-        <v>1.043112637178108</v>
+        <v>1.043147833764581</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.419461398736331</v>
+        <v>4.420101039448081</v>
       </c>
       <c r="E13" t="n">
-        <v>230.3987129741448</v>
+        <v>226.1382981373051</v>
       </c>
       <c r="F13" t="n">
-        <v>1.448490825839879</v>
+        <v>1.455602944591409</v>
       </c>
       <c r="G13" t="n">
-        <v>0.856087530095237</v>
+        <v>0.8561053176201402</v>
       </c>
       <c r="H13" t="n">
-        <v>1.69198916573255</v>
+        <v>1.700261538659511</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6013622032977989</v>
+        <v>0.6013673011015777</v>
       </c>
       <c r="N13" t="n">
-        <v>1.044031900633164</v>
+        <v>1.04407319442985</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.309340459615998</v>
+        <v>4.315879410064803</v>
       </c>
       <c r="E14" t="n">
-        <v>113.3512641930019</v>
+        <v>109.1039033182615</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4386143921516669</v>
+        <v>-0.4356392965557774</v>
       </c>
       <c r="G14" t="n">
-        <v>0.840471211304512</v>
+        <v>0.8404875247264585</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5218672409622274</v>
+        <v>-0.5183173857310478</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602075514109204</v>
+        <v>0.76019302907997</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295729930285334</v>
+        <v>1.295743669353542</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.834645654051984</v>
+        <v>3.82465058789267</v>
       </c>
       <c r="E15" t="n">
-        <v>198.0237132054522</v>
+        <v>143.7621737542303</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1220440214120906</v>
+        <v>0.3555081400635369</v>
       </c>
       <c r="G15" t="n">
-        <v>0.787541354562683</v>
+        <v>0.9541866976614785</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1549683971578368</v>
+        <v>0.3725771287053326</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J15" t="n">
         <v>277</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7131909116137266</v>
+        <v>0.5149636903383635</v>
       </c>
       <c r="N15" t="n">
-        <v>1.139039114068816</v>
+        <v>0.9964922085179024</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.799609482216328</v>
+        <v>3.816522491606297</v>
       </c>
       <c r="E16" t="n">
-        <v>148.8216820974102</v>
+        <v>196.621851780569</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3389706699920241</v>
+        <v>-0.1256178779380555</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9541601721839739</v>
+        <v>0.787556796450696</v>
       </c>
       <c r="H16" t="n">
-        <v>0.355255521948852</v>
+        <v>-0.1595032618652788</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J16" t="n">
         <v>277</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5150029151352268</v>
+        <v>0.7131860283093054</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9965301464712488</v>
+        <v>1.139065377536574</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.528629243336894</v>
+        <v>3.526784537207538</v>
       </c>
       <c r="E17" t="n">
-        <v>81.84170103935672</v>
+        <v>80.92271090804769</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1586195707008899</v>
+        <v>-0.155894483136813</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7528743902266241</v>
+        <v>0.7528831512766189</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2106853052248777</v>
+        <v>-0.2070633176907626</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7203886057393851</v>
+        <v>0.7203845581310678</v>
       </c>
       <c r="N17" t="n">
-        <v>1.09988892427678</v>
+        <v>1.099906869100799</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.980821346037951</v>
+        <v>2.985326584167027</v>
       </c>
       <c r="E18" t="n">
-        <v>71.9640831847193</v>
+        <v>69.21669685808432</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4892854504199434</v>
+        <v>-0.4864661956941588</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7376601712672348</v>
+        <v>0.7376689995590116</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6632938438026204</v>
+        <v>-0.6594640631299064</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7649347095950096</v>
+        <v>0.7649172388235513</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144300722806017</v>
+        <v>1.144300064824852</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.90650307911386</v>
+        <v>2.922032942003341</v>
       </c>
       <c r="E19" t="n">
-        <v>77.7486545413836</v>
+        <v>77.54781601120187</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08181517509863512</v>
+        <v>0.09170036911722423</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4758030316164224</v>
+        <v>0.4756696957158519</v>
       </c>
       <c r="H19" t="n">
-        <v>0.171951773448539</v>
+        <v>0.1927816086312187</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.715675069905863</v>
+        <v>0.7157755342493296</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6905618199957853</v>
+        <v>0.6904723230648991</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.548382412615672</v>
+        <v>2.556059879627186</v>
       </c>
       <c r="E20" t="n">
-        <v>111.4038394680242</v>
+        <v>108.9483652220335</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3297278793016962</v>
+        <v>-0.3252836132502523</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7695048279550933</v>
+        <v>0.7695143339397467</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.42849358096677</v>
+        <v>-0.422712870837468</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321073471556134</v>
+        <v>0.7320857530157798</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142472048718886</v>
+        <v>1.142464227290883</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-04.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-04.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.4936444427473</v>
+        <v>566.6140444390359</v>
       </c>
       <c r="E2" t="n">
-        <v>12262.48854787877</v>
+        <v>12359.19762379466</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5960126888649786</v>
+        <v>0.5922183170882784</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4931011992861996</v>
+        <v>0.4931093267282359</v>
       </c>
       <c r="H2" t="n">
-        <v>1.208702574091791</v>
+        <v>1.200987864126658</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>220.6613444177853</v>
+        <v>220.3031588335125</v>
       </c>
       <c r="E3" t="n">
-        <v>4547.455237789544</v>
+        <v>4489.909792789472</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2285719991414028</v>
+        <v>0.2250512595839764</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5908553155847328</v>
+        <v>0.5908582592108058</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3868493573848943</v>
+        <v>0.3808887429018452</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907309152877282</v>
+        <v>0.8907333384390008</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067312545204223</v>
+        <v>1.067303174456386</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.23187192500801</v>
+        <v>37.14573170162076</v>
       </c>
       <c r="E4" t="n">
-        <v>399.0629505598425</v>
+        <v>392.0895346328194</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3224208869507588</v>
+        <v>-0.3246300148199273</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5562326512300044</v>
+        <v>0.5562047341352612</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.579651133815653</v>
+        <v>-0.5836520167787386</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7369981739681813</v>
+        <v>0.7370020586153263</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8313556098655112</v>
+        <v>0.8313045644241005</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34.84155883497539</v>
+        <v>34.6953297792045</v>
       </c>
       <c r="E5" t="n">
-        <v>1189.695302143153</v>
+        <v>1142.997441290386</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5971118518413923</v>
+        <v>0.5847272410550213</v>
       </c>
       <c r="G5" t="n">
-        <v>1.09608356074647</v>
+        <v>1.096131992572082</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5447685497944509</v>
+        <v>0.5334460129048461</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4743722328466547</v>
+        <v>0.4743977596725915</v>
       </c>
       <c r="N5" t="n">
-        <v>1.054452122303663</v>
+        <v>1.0545380778576</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.42292453444059</v>
+        <v>10.40415301041506</v>
       </c>
       <c r="E6" t="n">
-        <v>332.3116084024765</v>
+        <v>322.5155325181331</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5054178925642967</v>
+        <v>-0.506995053064893</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8078636145023161</v>
+        <v>0.8078230498928327</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6256227950997137</v>
+        <v>-0.627606569448782</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6671152459309835</v>
+        <v>0.6670906356705639</v>
       </c>
       <c r="N6" t="n">
-        <v>1.092956445142617</v>
+        <v>1.092843235064866</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.27455902691923</v>
+        <v>10.24510370365168</v>
       </c>
       <c r="E7" t="n">
-        <v>284.7715639480708</v>
+        <v>276.2928099589569</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3456674819209137</v>
+        <v>-0.3488926043437829</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7079059188228215</v>
+        <v>0.7078752494863546</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4882957928868923</v>
+        <v>-0.4928730091876285</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7503331456014539</v>
+        <v>0.7503473745973279</v>
       </c>
       <c r="N7" t="n">
-        <v>1.077193232604415</v>
+        <v>1.077149236901871</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.279763948836955</v>
+        <v>9.254607729463391</v>
       </c>
       <c r="E8" t="n">
-        <v>332.9519268799259</v>
+        <v>325.8518879842953</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3685496608853822</v>
+        <v>-0.3718077517297347</v>
       </c>
       <c r="G8" t="n">
-        <v>1.159078031484617</v>
+        <v>1.159026709340072</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.317967945965917</v>
+        <v>-0.3207930833116305</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7373825456542384</v>
+        <v>0.7373711579643534</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733282966468644</v>
+        <v>1.733150886534967</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.951985251490613</v>
+        <v>6.936091502873055</v>
       </c>
       <c r="E9" t="n">
-        <v>175.6766051158071</v>
+        <v>173.2593885646715</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3118877084735936</v>
+        <v>0.3063300116479843</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4802207050252142</v>
+        <v>0.4801781009651059</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6494674328072084</v>
+        <v>0.6379508166496852</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6738597909511426</v>
+        <v>0.6738906871193286</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6562576289961132</v>
+        <v>0.6562186778052291</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.214101503947482</v>
+        <v>6.216969579150866</v>
       </c>
       <c r="E10" t="n">
-        <v>281.3587070836348</v>
+        <v>274.2016147145795</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3272731217324214</v>
+        <v>-0.327803797289954</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9482714351222369</v>
+        <v>0.9482712825043652</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.345125994109729</v>
+        <v>-0.3456856738550922</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7137128167814666</v>
+        <v>0.7137030777304881</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372524500070581</v>
+        <v>1.372482928557127</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.096350869484572</v>
+        <v>6.10602244590681</v>
       </c>
       <c r="E11" t="n">
-        <v>634.0259415106566</v>
+        <v>630.4982740276489</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7224447427470615</v>
+        <v>0.7221716583980458</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8190282832630276</v>
+        <v>0.8190274482056081</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8820754514957957</v>
+        <v>0.8817429256861148</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6622882721764796</v>
+        <v>0.662253447171599</v>
       </c>
       <c r="N11" t="n">
-        <v>1.100043616545955</v>
+        <v>1.099966521625444</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.044602292046744</v>
+        <v>6.07185546917021</v>
       </c>
       <c r="E12" t="n">
-        <v>102.6442912919572</v>
+        <v>101.0126229841787</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3089588336275628</v>
+        <v>-0.3102331040387807</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6518033200143509</v>
+        <v>0.651791668290524</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4740062287819589</v>
+        <v>-0.4759697294880119</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7891605213836451</v>
+        <v>0.7891409699076904</v>
       </c>
       <c r="N12" t="n">
-        <v>1.043147833764581</v>
+        <v>1.043086150297071</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.420101039448081</v>
+        <v>4.409505754516961</v>
       </c>
       <c r="E13" t="n">
-        <v>226.1382981373051</v>
+        <v>217.7684035969584</v>
       </c>
       <c r="F13" t="n">
-        <v>1.455602944591409</v>
+        <v>1.447068999114891</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8561053176201402</v>
+        <v>0.8560848705754405</v>
       </c>
       <c r="H13" t="n">
-        <v>1.700261538659511</v>
+        <v>1.690333574219346</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6013673011015777</v>
+        <v>0.6013576450320379</v>
       </c>
       <c r="N13" t="n">
-        <v>1.04407319442985</v>
+        <v>1.04401428610684</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.315879410064803</v>
+        <v>4.310599013480134</v>
       </c>
       <c r="E14" t="n">
-        <v>109.1039033182615</v>
+        <v>106.7769978284447</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4356392965557774</v>
+        <v>-0.438019676415092</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8404875247264585</v>
+        <v>0.8404724755887681</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5183173857310478</v>
+        <v>-0.5211588590194465</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.76019302907997</v>
+        <v>0.7601941820123835</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295743669353542</v>
+        <v>1.295701077737375</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.82465058789267</v>
+        <v>3.835813514941813</v>
       </c>
       <c r="E15" t="n">
-        <v>143.7621737542303</v>
+        <v>141.2081286970355</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3555081400635369</v>
+        <v>0.3580567042405445</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9541866976614785</v>
+        <v>0.9542013526204235</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3725771287053326</v>
+        <v>0.3752422937331317</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5149636903383635</v>
+        <v>0.5149032015578013</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9964922085179024</v>
+        <v>0.9963740387044419</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.816522491606297</v>
+        <v>3.823656671681257</v>
       </c>
       <c r="E16" t="n">
-        <v>196.621851780569</v>
+        <v>192.3699693987575</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1256178779380555</v>
+        <v>-0.1222065456582078</v>
       </c>
       <c r="G16" t="n">
-        <v>0.787556796450696</v>
+        <v>0.7875417151478332</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1595032618652788</v>
+        <v>-0.1551746952671171</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7131860283093054</v>
+        <v>0.713189833570502</v>
       </c>
       <c r="N16" t="n">
-        <v>1.139065377536574</v>
+        <v>1.13903086863668</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.526784537207538</v>
+        <v>3.527915184285979</v>
       </c>
       <c r="E17" t="n">
-        <v>80.92271090804769</v>
+        <v>73.30945502893786</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.155894483136813</v>
+        <v>-0.1575297906289629</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7528831512766189</v>
+        <v>0.7528766412652602</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2070633176907626</v>
+        <v>-0.2092371870698809</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7203845581310678</v>
+        <v>0.7203715777882609</v>
       </c>
       <c r="N17" t="n">
-        <v>1.099906869100799</v>
+        <v>1.09985941159674</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.985326584167027</v>
+        <v>2.972324428312743</v>
       </c>
       <c r="E18" t="n">
-        <v>69.21669685808432</v>
+        <v>69.97980103437533</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4864661956941588</v>
+        <v>-0.4905372503599044</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7376689995590116</v>
+        <v>0.7376661205165637</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6594640631299064</v>
+        <v>-0.6649854679735014</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7649172388235513</v>
+        <v>0.7649426839205057</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144300064824852</v>
+        <v>1.144314802985163</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.922032942003341</v>
+        <v>2.954682077653614</v>
       </c>
       <c r="E19" t="n">
-        <v>77.54781601120187</v>
+        <v>80.59137080232182</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09170036911722423</v>
+        <v>0.1070199913907075</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4756696957158519</v>
+        <v>0.4757163466635244</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1927816086312187</v>
+        <v>0.2249659742434772</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7157755342493296</v>
+        <v>0.7155771752792766</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6904723230648991</v>
+        <v>0.6903372966767487</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.556059879627186</v>
+        <v>2.557543260631891</v>
       </c>
       <c r="E20" t="n">
-        <v>108.9483652220335</v>
+        <v>108.4028724615599</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3252836132502523</v>
+        <v>-0.325777770119575</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7695143339397467</v>
+        <v>0.7695111763352327</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.422712870837468</v>
+        <v>-0.4233567752336997</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320857530157798</v>
+        <v>0.7320592140810868</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142464227290883</v>
+        <v>1.142399294518</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-04.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-04.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>566.6140444390359</v>
+        <v>567.805658516419</v>
       </c>
       <c r="E2" t="n">
-        <v>12359.19762379466</v>
+        <v>12587.49992133875</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5922183170882784</v>
+        <v>0.5960508379214156</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4931093267282359</v>
+        <v>0.4931011612422277</v>
       </c>
       <c r="H2" t="n">
-        <v>1.200987864126658</v>
+        <v>1.208780032924351</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>220.3031588335125</v>
+        <v>220.93700574452</v>
       </c>
       <c r="E3" t="n">
-        <v>4489.909792789472</v>
+        <v>4655.390411612017</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2250512595839764</v>
+        <v>0.2294085326355881</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5908582592108058</v>
+        <v>0.5908561510349439</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3808887429018452</v>
+        <v>0.3882646093025452</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907333384390008</v>
+        <v>0.890727948664177</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067303174456386</v>
+        <v>1.067310581952644</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.14573170162076</v>
+        <v>37.23384595084524</v>
       </c>
       <c r="E4" t="n">
-        <v>392.0895346328194</v>
+        <v>388.6619248767203</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3246300148199273</v>
+        <v>-0.3231574561471369</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5562047341352612</v>
+        <v>0.5562217378589633</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5836520167787386</v>
+        <v>-0.5809867435081749</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7370020586153263</v>
+        <v>0.7370163007460677</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8313045644241005</v>
+        <v>0.8313598098179769</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34.6953297792045</v>
+        <v>34.94783320189061</v>
       </c>
       <c r="E5" t="n">
-        <v>1142.997441290386</v>
+        <v>1144.91669685971</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5847272410550213</v>
+        <v>0.6015632726301803</v>
       </c>
       <c r="G5" t="n">
-        <v>1.096131992572082</v>
+        <v>1.096076182061384</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5334460129048461</v>
+        <v>0.548833450151999</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4743977596725915</v>
+        <v>0.474371297100992</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0545380778576</v>
+        <v>1.054443025232598</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.40415301041506</v>
+        <v>10.43880273496228</v>
       </c>
       <c r="E6" t="n">
-        <v>322.5155325181331</v>
+        <v>320.2156058945909</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.506995053064893</v>
+        <v>-0.5051549144481353</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8078230498928327</v>
+        <v>0.8078713110637794</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.627606569448782</v>
+        <v>-0.6252913150028354</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6670906356705639</v>
+        <v>0.6671085792261934</v>
       </c>
       <c r="N6" t="n">
-        <v>1.092843235064866</v>
+        <v>1.09295601974179</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.24510370365168</v>
+        <v>10.32243173147176</v>
       </c>
       <c r="E7" t="n">
-        <v>276.2928099589569</v>
+        <v>253.6036147240265</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3488926043437829</v>
+        <v>-0.3427322224874686</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7078752494863546</v>
+        <v>0.7079563751467592</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4928730091876285</v>
+        <v>-0.4841148897294982</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7503473745973279</v>
+        <v>0.7502701396959787</v>
       </c>
       <c r="N7" t="n">
-        <v>1.077149236901871</v>
+        <v>1.077179634178746</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.254607729463391</v>
+        <v>9.392735872450778</v>
       </c>
       <c r="E8" t="n">
-        <v>325.8518879842953</v>
+        <v>338.9043074879779</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3718077517297347</v>
+        <v>-0.3591146413384583</v>
       </c>
       <c r="G8" t="n">
-        <v>1.159026709340072</v>
+        <v>1.159325711190704</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3207930833116305</v>
+        <v>-0.3097616466813489</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7373711579643534</v>
+        <v>0.7372051125351643</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733150886534967</v>
+        <v>1.733236318548059</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.936091502873055</v>
+        <v>6.946407186903082</v>
       </c>
       <c r="E9" t="n">
-        <v>173.2593885646715</v>
+        <v>172.0302771201525</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3063300116479843</v>
+        <v>0.3092193040724225</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4801781009651059</v>
+        <v>0.4801967079265563</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6379508166496852</v>
+        <v>0.6439429903790929</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6738906871193286</v>
+        <v>0.6739008746293506</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6562186778052291</v>
+        <v>0.6562648943081184</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.216969579150866</v>
+        <v>6.262010250068689</v>
       </c>
       <c r="E10" t="n">
-        <v>274.2016147145795</v>
+        <v>272.7684201782693</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.327803797289954</v>
+        <v>-0.3210301334338813</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9482712825043652</v>
+        <v>0.9483100714741388</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3456856738550922</v>
+        <v>-0.3385286554373962</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7137030777304881</v>
+        <v>0.7136684408102502</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372482928557127</v>
+        <v>1.372495186198008</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.10602244590681</v>
+        <v>6.127161405241687</v>
       </c>
       <c r="E11" t="n">
-        <v>630.4982740276489</v>
+        <v>634.6052234312107</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7221716583980458</v>
+        <v>0.7279086207576826</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8190274482056081</v>
+        <v>0.8190498741195849</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8817429256861148</v>
+        <v>0.8887231947140313</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.662253447171599</v>
+        <v>0.6622649941805061</v>
       </c>
       <c r="N11" t="n">
-        <v>1.099966521625444</v>
+        <v>1.100034035107235</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.07185546917021</v>
+        <v>6.103975062967385</v>
       </c>
       <c r="E12" t="n">
-        <v>101.0126229841787</v>
+        <v>102.4965647813868</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3102331040387807</v>
+        <v>-0.3047679575493734</v>
       </c>
       <c r="G12" t="n">
-        <v>0.651791668290524</v>
+        <v>0.6518693491586353</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4759697294880119</v>
+        <v>-0.4675292034250973</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7891409699076904</v>
+        <v>0.7890663229620537</v>
       </c>
       <c r="N12" t="n">
-        <v>1.043086150297071</v>
+        <v>1.043129059149785</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.409505754516961</v>
+        <v>4.433765270346048</v>
       </c>
       <c r="E13" t="n">
-        <v>217.7684035969584</v>
+        <v>215.2820219937961</v>
       </c>
       <c r="F13" t="n">
-        <v>1.447068999114891</v>
+        <v>1.4641440464911</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8560848705754405</v>
+        <v>0.8561365399427007</v>
       </c>
       <c r="H13" t="n">
-        <v>1.690333574219346</v>
+        <v>1.710175863524167</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6013576450320379</v>
+        <v>0.6013393264047269</v>
       </c>
       <c r="N13" t="n">
-        <v>1.04401428610684</v>
+        <v>1.044062782051969</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.310599013480134</v>
+        <v>4.339548628040431</v>
       </c>
       <c r="E14" t="n">
-        <v>106.7769978284447</v>
+        <v>105.2315652764317</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.438019676415092</v>
+        <v>-0.4320641851374052</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8404724755887681</v>
+        <v>0.8405400724691104</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5211588590194465</v>
+        <v>-0.5140316319104268</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601941820123835</v>
+        <v>0.760133939518126</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295701077737375</v>
+        <v>1.295724055889894</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.835813514941813</v>
+        <v>3.861115567965369</v>
       </c>
       <c r="E15" t="n">
-        <v>141.2081286970355</v>
+        <v>135.3787247820919</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3580567042405445</v>
+        <v>0.3695395028408506</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9542013526204235</v>
+        <v>0.9543021887075451</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3752422937331317</v>
+        <v>0.3872353089133482</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5149032015578013</v>
+        <v>0.5148845680628787</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9963740387044419</v>
+        <v>0.9964597710463996</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.823656671681257</v>
+        <v>3.848054532022697</v>
       </c>
       <c r="E16" t="n">
-        <v>192.3699693987575</v>
+        <v>195.2181770092252</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1222065456582078</v>
+        <v>-0.1171649240757154</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7875417151478332</v>
+        <v>0.7875456528441613</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1551746952671171</v>
+        <v>-0.1487722313653605</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.713189833570502</v>
+        <v>0.7131766989198327</v>
       </c>
       <c r="N16" t="n">
-        <v>1.13903086863668</v>
+        <v>1.139034447879059</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.527915184285979</v>
+        <v>3.553180843817982</v>
       </c>
       <c r="E17" t="n">
-        <v>73.30945502893786</v>
+        <v>73.18313974272482</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1575297906289629</v>
+        <v>-0.1477064982819039</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7528766412652602</v>
+        <v>0.7529720982095729</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2092371870698809</v>
+        <v>-0.1961646369541744</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7203715777882609</v>
+        <v>0.7202794226560583</v>
       </c>
       <c r="N17" t="n">
-        <v>1.09985941159674</v>
+        <v>1.099876355610713</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.972324428312743</v>
+        <v>2.985314543519219</v>
       </c>
       <c r="E18" t="n">
-        <v>69.97980103437533</v>
+        <v>70.91916980001098</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4905372503599044</v>
+        <v>-0.4877196597242591</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7376661205165637</v>
+        <v>0.7376612786015135</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6649854679735014</v>
+        <v>-0.6611702062617367</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7649426839205057</v>
+        <v>0.7649307325589557</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144314802985163</v>
+        <v>1.144308362202068</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.954682077653614</v>
+        <v>2.928249905846049</v>
       </c>
       <c r="E19" t="n">
-        <v>80.59137080232182</v>
+        <v>93.33215713944827</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1070199913907075</v>
+        <v>0.09170036911722423</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4757163466635244</v>
+        <v>0.4756696957158519</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2249659742434772</v>
+        <v>0.1927816086312187</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7155771752792766</v>
+        <v>0.7157752184690459</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6903372966767487</v>
+        <v>0.69047207171931</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.557543260631891</v>
+        <v>2.570339303713468</v>
       </c>
       <c r="E20" t="n">
-        <v>108.4028724615599</v>
+        <v>108.7610240028806</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.325777770119575</v>
+        <v>-0.3208322781498689</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7695111763352327</v>
+        <v>0.7695663911317229</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4233567752336997</v>
+        <v>-0.4169000645649995</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320592140810868</v>
+        <v>0.7320230011949991</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142399294518</v>
+        <v>1.142443667818329</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-04.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-04.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.805658516419</v>
+        <v>568.4559132341903</v>
       </c>
       <c r="E2" t="n">
-        <v>12587.49992133875</v>
+        <v>11941.26524568298</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5960508379214156</v>
+        <v>0.6004920251613159</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4931011612422277</v>
+        <v>0.493102666925332</v>
       </c>
       <c r="H2" t="n">
-        <v>1.208780032924351</v>
+        <v>1.21778295969396</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>220.93700574452</v>
+        <v>221.6675148848934</v>
       </c>
       <c r="E3" t="n">
-        <v>4655.390411612017</v>
+        <v>4807.960887200908</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2294085326355881</v>
+        <v>0.2366612943086726</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5908561510349439</v>
+        <v>0.5908880424101196</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3882646093025452</v>
+        <v>0.4005179954960271</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.890727948664177</v>
+        <v>0.8907130410334083</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067310581952644</v>
+        <v>1.067347066782528</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.23384595084524</v>
+        <v>37.35176592602844</v>
       </c>
       <c r="E4" t="n">
-        <v>388.6619248767203</v>
+        <v>377.2753073034737</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3231574561471369</v>
+        <v>-0.3202100212266098</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5562217378589633</v>
+        <v>0.5562750362026173</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5809867435081749</v>
+        <v>-0.5756325565362539</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7370163007460677</v>
+        <v>0.7370165063578074</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8313598098179769</v>
+        <v>0.8314371656363349</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34.94783320189061</v>
+        <v>34.9752161751052</v>
       </c>
       <c r="E5" t="n">
-        <v>1144.91669685971</v>
+        <v>1099.27684082417</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6015632726301803</v>
+        <v>0.6037901026426948</v>
       </c>
       <c r="G5" t="n">
-        <v>1.096076182061384</v>
+        <v>1.096074475337834</v>
       </c>
       <c r="H5" t="n">
-        <v>0.548833450151999</v>
+        <v>0.5508659459080951</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.474371297100992</v>
+        <v>0.4743643474921569</v>
       </c>
       <c r="N5" t="n">
-        <v>1.054443025232598</v>
+        <v>1.054422715939541</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.43880273496228</v>
+        <v>10.45339005459828</v>
       </c>
       <c r="E6" t="n">
-        <v>320.2156058945909</v>
+        <v>309.2466086788245</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5051549144481353</v>
+        <v>-0.5037517955847179</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8078713110637794</v>
+        <v>0.8079168744377211</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6252913150028354</v>
+        <v>-0.6235193390846178</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6671085792261934</v>
+        <v>0.6671606144978551</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09295601974179</v>
+        <v>1.093099580608587</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.32243173147176</v>
+        <v>10.35005809882552</v>
       </c>
       <c r="E7" t="n">
-        <v>253.6036147240265</v>
+        <v>246.2991640258635</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3427322224874686</v>
+        <v>-0.339499783200951</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7079563751467592</v>
+        <v>0.7080367040601407</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4841148897294982</v>
+        <v>-0.4794946098897633</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7502701396959787</v>
+        <v>0.7502779402633395</v>
       </c>
       <c r="N7" t="n">
-        <v>1.077179634178746</v>
+        <v>1.077309768502077</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.392735872450778</v>
+        <v>9.433830248992782</v>
       </c>
       <c r="E8" t="n">
-        <v>338.9043074879779</v>
+        <v>358.4893215346698</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3591146413384583</v>
+        <v>-0.3540203091808426</v>
       </c>
       <c r="G8" t="n">
-        <v>1.159325711190704</v>
+        <v>1.159520230764345</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3097616466813489</v>
+        <v>-0.3053161987070082</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7372051125351643</v>
+        <v>0.7372178179958756</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733236318548059</v>
+        <v>1.733551716068096</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.946407186903082</v>
+        <v>6.952661747349972</v>
       </c>
       <c r="E9" t="n">
-        <v>172.0302771201525</v>
+        <v>165.1788348245725</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3092193040724225</v>
+        <v>0.3121101346223794</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4801967079265563</v>
+        <v>0.4802230003494322</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6439429903790929</v>
+        <v>0.6499275011719009</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6739008746293506</v>
+        <v>0.6739312672730889</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6562648943081184</v>
+        <v>0.6563284218622664</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.262010250068689</v>
+        <v>6.269753198024003</v>
       </c>
       <c r="E10" t="n">
-        <v>272.7684201782693</v>
+        <v>262.6711052588458</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3210301334338813</v>
+        <v>-0.3197000462742569</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9483100714741388</v>
+        <v>0.9483270526710991</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3385286554373962</v>
+        <v>-0.3371200319275675</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7136684408102502</v>
+        <v>0.7137031886498197</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372495186198008</v>
+        <v>1.372582398701033</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.127161405241687</v>
+        <v>6.140357698220473</v>
       </c>
       <c r="E11" t="n">
-        <v>634.6052234312107</v>
+        <v>634.1254508483132</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7279086207576826</v>
+        <v>0.7358386467454023</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8190498741195849</v>
+        <v>0.8190977231194515</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8887231947140313</v>
+        <v>0.8983526946492228</v>
       </c>
       <c r="I11" t="n">
         <v>0.3268819295856837</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6622649941805061</v>
+        <v>0.6622856988976025</v>
       </c>
       <c r="N11" t="n">
-        <v>1.100034035107235</v>
+        <v>1.100129332911811</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.103975062967385</v>
+        <v>6.08581879970682</v>
       </c>
       <c r="E12" t="n">
-        <v>102.4965647813868</v>
+        <v>99.3127268784974</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3047679575493734</v>
+        <v>-0.3042208714434061</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6518693491586353</v>
+        <v>0.6518810975936769</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4675292034250973</v>
+        <v>-0.4666815352775111</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890663229620537</v>
+        <v>0.7891338955563253</v>
       </c>
       <c r="N12" t="n">
-        <v>1.043129059149785</v>
+        <v>1.043234004778821</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.433765270346048</v>
+        <v>4.419256606716038</v>
       </c>
       <c r="E13" t="n">
-        <v>215.2820219937961</v>
+        <v>206.8080603923291</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4641440464911</v>
+        <v>1.451335076494578</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8561365399427007</v>
+        <v>0.8560937471302671</v>
       </c>
       <c r="H13" t="n">
-        <v>1.710175863524167</v>
+        <v>1.695299237215122</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6013393264047269</v>
+        <v>0.6014101022415587</v>
       </c>
       <c r="N13" t="n">
-        <v>1.044062782051969</v>
+        <v>1.044130284673427</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.339548628040431</v>
+        <v>4.346517671459702</v>
       </c>
       <c r="E14" t="n">
-        <v>105.2315652764317</v>
+        <v>103.4060934193344</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4320641851374052</v>
+        <v>-0.4314678044360887</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8405400724691104</v>
+        <v>0.840552327030597</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5140316319104268</v>
+        <v>-0.513314627252686</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.760133939518126</v>
+        <v>0.7601865360368566</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295724055889894</v>
+        <v>1.295828647261942</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.861115567965369</v>
+        <v>3.862949153271393</v>
       </c>
       <c r="E15" t="n">
-        <v>135.3787247820919</v>
+        <v>195.8201712931748</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3695395028408506</v>
+        <v>-0.1116274117647377</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9543021887075451</v>
+        <v>0.7875858908342884</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3872353089133482</v>
+        <v>-0.1417336357390696</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J15" t="n">
         <v>277</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5148845680628787</v>
+        <v>0.7131785313525063</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9964597710463996</v>
+        <v>1.139092093014794</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.848054532022697</v>
+        <v>3.851628428770812</v>
       </c>
       <c r="E16" t="n">
-        <v>195.2181770092252</v>
+        <v>129.4727861603144</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1171649240757154</v>
+        <v>0.3657093139665428</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7875456528441613</v>
+        <v>0.9542622338144094</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1487722313653605</v>
+        <v>0.3832377526926924</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J16" t="n">
         <v>277</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7131766989198327</v>
+        <v>0.5149822637515465</v>
       </c>
       <c r="N16" t="n">
-        <v>1.139034447879059</v>
+        <v>0.9966040712101171</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.553180843817982</v>
+        <v>3.571131702479639</v>
       </c>
       <c r="E17" t="n">
-        <v>73.18313974272482</v>
+        <v>74.58103215109189</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1477064982819039</v>
+        <v>-0.1420548225406851</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7529720982095729</v>
+        <v>0.7530880384294771</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1961646369541744</v>
+        <v>-0.1886297687544374</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7202794226560583</v>
+        <v>0.7202688564520772</v>
       </c>
       <c r="N17" t="n">
-        <v>1.099876355610713</v>
+        <v>1.100026214884525</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.985314543519219</v>
+        <v>2.994333009044656</v>
       </c>
       <c r="E18" t="n">
-        <v>70.91916980001098</v>
+        <v>70.01679040807684</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4877196597242591</v>
+        <v>-0.4849767486016024</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7376612786015135</v>
+        <v>0.7376860591220413</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6611702062617367</v>
+        <v>-0.6574297326138961</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7649307325589557</v>
+        <v>0.7649327627781515</v>
       </c>
       <c r="N18" t="n">
-        <v>1.144308362202068</v>
+        <v>1.14434634634129</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.928249905846049</v>
+        <v>2.907441782753369</v>
       </c>
       <c r="E19" t="n">
-        <v>93.33215713944827</v>
+        <v>94.75606567765472</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09170036911722423</v>
+        <v>0.08271293271814728</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4756696957158519</v>
+        <v>0.4757856032337081</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1927816086312187</v>
+        <v>0.1738449674727091</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7157752184690459</v>
+        <v>0.7155096738706108</v>
       </c>
       <c r="N19" t="n">
-        <v>0.69047207171931</v>
+        <v>0.6903819927091003</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.570339303713468</v>
+        <v>2.568493902213042</v>
       </c>
       <c r="E20" t="n">
-        <v>108.7610240028806</v>
+        <v>106.5096863492947</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3208322781498689</v>
+        <v>-0.3218220733994799</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7695663911317229</v>
+        <v>0.769551145933786</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4169000645649995</v>
+        <v>-0.4181945217026162</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320230011949991</v>
+        <v>0.7320927954233103</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142443667818329</v>
+        <v>1.142526470523404</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-04.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-04.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>568.4559132341903</v>
+        <v>568.4137608653393</v>
       </c>
       <c r="E2" t="n">
-        <v>11941.26524568298</v>
+        <v>11422.46316134523</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6004920251613159</v>
+        <v>0.5979924112107566</v>
       </c>
       <c r="G2" t="n">
-        <v>0.493102666925332</v>
+        <v>0.4931003721221172</v>
       </c>
       <c r="H2" t="n">
-        <v>1.21778295969396</v>
+        <v>1.212719448247877</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>221.6675148848934</v>
+        <v>221.5162571779199</v>
       </c>
       <c r="E3" t="n">
-        <v>4807.960887200908</v>
+        <v>4626.930862234844</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2366612943086726</v>
+        <v>0.2338576714885459</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5908880424101196</v>
+        <v>0.5908704797006152</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4005179954960271</v>
+        <v>0.3957849977664104</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907130410334083</v>
+        <v>0.8907135559013049</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067347066782528</v>
+        <v>1.067320926541314</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.35176592602844</v>
+        <v>37.34644138561545</v>
       </c>
       <c r="E4" t="n">
-        <v>377.2753073034737</v>
+        <v>362.9199324082375</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3202100212266098</v>
+        <v>-0.3209471693819406</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5562750362026173</v>
+        <v>0.5562593005173475</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5756325565362539</v>
+        <v>-0.5769740282696298</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7370165063578074</v>
+        <v>0.7369921677648031</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8314371656363349</v>
+        <v>0.8313900595193344</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>34.9752161751052</v>
+        <v>34.99739530479815</v>
       </c>
       <c r="E5" t="n">
-        <v>1099.27684082417</v>
+        <v>1068.058139955711</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6037901026426948</v>
+        <v>0.600609145317835</v>
       </c>
       <c r="G5" t="n">
-        <v>1.096074475337834</v>
+        <v>1.096077318132103</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5508659459080951</v>
+        <v>0.5479623885852984</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4743643474921569</v>
+        <v>0.4743672133318219</v>
       </c>
       <c r="N5" t="n">
-        <v>1.054422715939541</v>
+        <v>1.054436728086219</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.45339005459828</v>
+        <v>10.48572293559086</v>
       </c>
       <c r="E6" t="n">
-        <v>309.2466086788245</v>
+        <v>287.8276727303302</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5037517955847179</v>
+        <v>-0.5029621205152561</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8079168744377211</v>
+        <v>0.8079458452288366</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6235193390846178</v>
+        <v>-0.6225195951998501</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6671606144978551</v>
+        <v>0.6670856101149844</v>
       </c>
       <c r="N6" t="n">
-        <v>1.093099580608587</v>
+        <v>1.093020970121816</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.35005809882552</v>
+        <v>10.36762954632847</v>
       </c>
       <c r="E7" t="n">
-        <v>246.2991640258635</v>
+        <v>235.6418490185092</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.339499783200951</v>
+        <v>-0.3392057355919911</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7080367040601407</v>
+        <v>0.7080452961274256</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4794946098897633</v>
+        <v>-0.4790734963529012</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7502779402633395</v>
+        <v>0.7502127252721628</v>
       </c>
       <c r="N7" t="n">
-        <v>1.077309768502077</v>
+        <v>1.077234212859898</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.433830248992782</v>
+        <v>9.437964443838181</v>
       </c>
       <c r="E8" t="n">
-        <v>358.4893215346698</v>
+        <v>352.1333829264466</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3540203091808426</v>
+        <v>-0.3562047850178353</v>
       </c>
       <c r="G8" t="n">
-        <v>1.159520230764345</v>
+        <v>1.159431625364668</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3053161987070082</v>
+        <v>-0.3072236233902975</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7372178179958756</v>
+        <v>0.7371925247866775</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733551716068096</v>
+        <v>1.73336784059134</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.952661747349972</v>
+        <v>6.947492268712973</v>
       </c>
       <c r="E9" t="n">
-        <v>165.1788348245725</v>
+        <v>163.3879694446985</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3121101346223794</v>
+        <v>0.3083301271130867</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4802230003494322</v>
+        <v>0.4801901640890656</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6499275011719009</v>
+        <v>0.6421000473801828</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6739312672730889</v>
+        <v>0.6739357026877819</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6563284218622664</v>
+        <v>0.656290917539566</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.269753198024003</v>
+        <v>6.285408873003532</v>
       </c>
       <c r="E10" t="n">
-        <v>262.6711052588458</v>
+        <v>257.2995266954513</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3197000462742569</v>
+        <v>-0.3191678357392449</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9483270526710991</v>
+        <v>0.9483347057741771</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3371200319275675</v>
+        <v>-0.3365561059781007</v>
       </c>
       <c r="I10" t="n">
         <v>0.6126386245816655</v>
@@ -976,45 +976,45 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.7137031886498197</v>
+        <v>0.7136711670584418</v>
       </c>
       <c r="N10" t="n">
-        <v>1.372582398701033</v>
+        <v>1.372538279213203</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>DOT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Litecoin</t>
+          <t>Polkadot</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.140357698220473</v>
+        <v>6.272126827249913</v>
       </c>
       <c r="E11" t="n">
-        <v>634.1254508483132</v>
+        <v>96.17510949331378</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7358386467454023</v>
+        <v>-0.3049502965258694</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8190977231194515</v>
+        <v>0.6518655938126439</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8983526946492228</v>
+        <v>-0.4678116154931115</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3268819295856837</v>
+        <v>0.4207389749702026</v>
       </c>
       <c r="J11" t="n">
         <v>277</v>
@@ -1030,45 +1030,45 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.6622856988976025</v>
+        <v>0.7891074255099088</v>
       </c>
       <c r="N11" t="n">
-        <v>1.100129332911811</v>
+        <v>1.043179055611407</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DOT</t>
+          <t>LTC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Polkadot</t>
+          <t>Litecoin</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.08581879970682</v>
+        <v>6.133527739725864</v>
       </c>
       <c r="E12" t="n">
-        <v>99.3127268784974</v>
+        <v>622.5472595686999</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3042208714434061</v>
+        <v>0.7303687263156171</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6518810975936769</v>
+        <v>0.8190626284840677</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4666815352775111</v>
+        <v>0.8917129178111733</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4207389749702026</v>
+        <v>0.3268819295856837</v>
       </c>
       <c r="J12" t="n">
         <v>277</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7891338955563253</v>
+        <v>0.6622765215955134</v>
       </c>
       <c r="N12" t="n">
-        <v>1.043234004778821</v>
+        <v>1.100072073007823</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.419256606716038</v>
+        <v>4.424277655385965</v>
       </c>
       <c r="E13" t="n">
-        <v>206.8080603923291</v>
+        <v>200.2877822602321</v>
       </c>
       <c r="F13" t="n">
-        <v>1.451335076494578</v>
+        <v>1.454180123023489</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8560937471302671</v>
+        <v>0.8561011614702854</v>
       </c>
       <c r="H13" t="n">
-        <v>1.695299237215122</v>
+        <v>1.698607814672335</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6014101022415587</v>
+        <v>0.6013895649248052</v>
       </c>
       <c r="N13" t="n">
-        <v>1.044130284673427</v>
+        <v>1.044108530708494</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.346517671459702</v>
+        <v>4.342528860253116</v>
       </c>
       <c r="E14" t="n">
-        <v>103.4060934193344</v>
+        <v>99.63023357706837</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4314678044360887</v>
+        <v>-0.4326604148905596</v>
       </c>
       <c r="G14" t="n">
-        <v>0.840552327030597</v>
+        <v>0.8405288168764931</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.513314627252686</v>
+        <v>-0.5147478661093122</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601865360368566</v>
+        <v>0.7601723849935147</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295828647261942</v>
+        <v>1.295774311893126</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.862949153271393</v>
+        <v>3.877785394070331</v>
       </c>
       <c r="E15" t="n">
-        <v>195.8201712931748</v>
+        <v>184.6739118370644</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1116274117647377</v>
+        <v>-0.1077135599599862</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7875858908342884</v>
+        <v>0.7876369154781026</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1417336357390696</v>
+        <v>-0.1367553473475823</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7131785313525063</v>
+        <v>0.7131073800159125</v>
       </c>
       <c r="N15" t="n">
-        <v>1.139092093014794</v>
+        <v>1.139057540725818</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.851628428770812</v>
+        <v>3.830854163293494</v>
       </c>
       <c r="E16" t="n">
-        <v>129.4727861603144</v>
+        <v>120.6497241412259</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3657093139665428</v>
+        <v>0.3529607306211247</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9542622338144094</v>
+        <v>0.9541748623260639</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3832377526926924</v>
+        <v>0.36991199889786</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5149822637515465</v>
+        <v>0.5149879794599482</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9966040712101171</v>
+        <v>0.9965285207269741</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.571131702479639</v>
+        <v>3.570210033801283</v>
       </c>
       <c r="E17" t="n">
-        <v>74.58103215109189</v>
+        <v>73.4835943929148</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1420548225406851</v>
+        <v>-0.1451552438266541</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7530880384294771</v>
+        <v>0.7530189373626812</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1886297687544374</v>
+        <v>-0.1927644002354513</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7202688564520772</v>
+        <v>0.7202713902027569</v>
       </c>
       <c r="N17" t="n">
-        <v>1.100026214884525</v>
+        <v>1.099934268005177</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.994333009044656</v>
+        <v>2.991338467167658</v>
       </c>
       <c r="E18" t="n">
-        <v>70.01679040807684</v>
+        <v>69.04568619138301</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4849767486016024</v>
+        <v>-0.4861527143259812</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7376860591220413</v>
+        <v>0.7376718790964983</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6574297326138961</v>
+        <v>-0.6590365284378493</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7649327627781515</v>
+        <v>0.7649268322862078</v>
       </c>
       <c r="N18" t="n">
-        <v>1.14434634634129</v>
+        <v>1.144320802913849</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.907441782753369</v>
+        <v>2.909427838049942</v>
       </c>
       <c r="E19" t="n">
-        <v>94.75606567765472</v>
+        <v>95.50739250135183</v>
       </c>
       <c r="F19" t="n">
-        <v>0.08271293271814728</v>
+        <v>0.0845089864013262</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4757856032337081</v>
+        <v>0.4757539298821333</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1738449674727091</v>
+        <v>0.1776317148284262</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7155096738706108</v>
+        <v>0.7156269486737649</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6903819927091003</v>
+        <v>0.6904523955151007</v>
       </c>
     </row>
     <row r="20">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.568493902213042</v>
+        <v>2.56844112627329</v>
       </c>
       <c r="E20" t="n">
-        <v>106.5096863492947</v>
+        <v>104.0505243726392</v>
       </c>
       <c r="F20" t="n">
         <v>-0.3218220733994799</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320927954233103</v>
+        <v>0.7320655187528499</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142526470523404</v>
+        <v>1.142489218635895</v>
       </c>
     </row>
   </sheetData>
